--- a/super.xlsx
+++ b/super.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
   <si>
     <t>Order ID</t>
   </si>
@@ -147,13 +147,40 @@
   </si>
   <si>
     <t>Total Profit</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>Total Sales</t>
+  </si>
+  <si>
+    <t>Total profit</t>
+  </si>
+  <si>
+    <t>Sales Rank</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,8 +210,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,6 +248,11 @@
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -233,13 +280,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2" applyAlignment="1">
@@ -258,11 +306,21 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="40% - Accent1" xfId="2" builtinId="31"/>
     <cellStyle name="40% - Accent5" xfId="3" builtinId="47"/>
     <cellStyle name="Input" xfId="1" builtinId="20"/>
+    <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -293,14 +351,52 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Performance by region</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.27044444444444443"/>
+          <c:y val="3.2407407407407406E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -329,17 +425,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.13513648293963254"/>
-          <c:y val="0.14393518518518519"/>
-          <c:w val="0.86486351706036746"/>
-          <c:h val="0.72088764946048411"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -349,11 +435,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$J$1</c:f>
+              <c:f>Sheet1!$M$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total Profit</c:v>
+                  <c:v>Total Sales</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -370,42 +456,48 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$I$2:$I$4</c:f>
+              <c:f>Sheet1!$L$3:$L$6</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>Furniture</c:v>
+                  <c:v>East</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Office Supplies</c:v>
+                  <c:v>West</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Technology</c:v>
+                  <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>South</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$J$2:$J$4</c:f>
+              <c:f>Sheet1!$M$3:$M$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>19000</c:v>
+                  <c:v>113800</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3400</c:v>
+                  <c:v>37000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>32700</c:v>
+                  <c:v>100500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>53000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-49C1-4742-847D-45BFBB4B084A}"/>
+              <c16:uniqueId val="{00000000-D17A-4061-9DBF-F9EA1653EAC1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -419,11 +511,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1757237823"/>
-        <c:axId val="1757230335"/>
+        <c:axId val="81036448"/>
+        <c:axId val="81040608"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1757237823"/>
+        <c:axId val="81036448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -466,7 +558,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1757230335"/>
+        <c:crossAx val="81040608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -474,7 +566,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1757230335"/>
+        <c:axId val="81040608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -525,7 +617,320 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1757237823"/>
+        <c:crossAx val="81036448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t> Profit Performance by Region</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$N$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total profit</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$L$3:$L$6</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>West</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>South</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$N$3:$N$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>19300</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1781-416E-B27C-F2DB9DE05832}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="78922608"/>
+        <c:axId val="78923024"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="78922608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="78923024"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="78923024"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="78922608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -614,7 +1019,550 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1122,19 +2070,19 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>607161</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>351129</xdr:rowOff>
+      <xdr:colOff>80466</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>131673</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>329184</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>351129</xdr:rowOff>
+      <xdr:colOff>234085</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>131673</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1144,6 +2092,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7314</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>117042</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>504748</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>117042</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1415,15 +2393,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.69921875" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="13.19921875" customWidth="1"/>
+    <col min="14" max="14" width="10.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1445,14 +2424,20 @@
       <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="I1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>40</v>
       </c>
+      <c r="L1" s="8" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -1473,6 +2458,9 @@
       </c>
       <c r="G2" s="3">
         <v>12000</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>12</v>
@@ -1481,8 +2469,20 @@
         <f>SUMIF($C$2:$C$16,I2,$G$2:$G$16)</f>
         <v>19000</v>
       </c>
+      <c r="L2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1503,6 +2503,9 @@
       </c>
       <c r="G3" s="3">
         <v>3500</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>17</v>
@@ -1511,8 +2514,23 @@
         <f>SUMIF($C$2:$C$16,I3,$G$2:$G$16)</f>
         <v>3400</v>
       </c>
+      <c r="L3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="11">
+        <f>SUMIF($H$2:$H$16,L3,$D$2:$D$16)</f>
+        <v>113800</v>
+      </c>
+      <c r="N3" s="11">
+        <f>SUMIF($H$2:$H$16,L3,$G$2:$G$16)</f>
+        <v>19300</v>
+      </c>
+      <c r="O3" s="11">
+        <f>_xlfn.RANK.EQ(M3,$M$3:$M$6,0)</f>
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -1533,6 +2551,9 @@
       </c>
       <c r="G4" s="3">
         <v>4500</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>9</v>
@@ -1541,8 +2562,20 @@
         <f>SUMIF($C$2:$C$16,I4,$G$2:$G$16)</f>
         <v>32700</v>
       </c>
+      <c r="L4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M4" s="11">
+        <v>37000</v>
+      </c>
+      <c r="N4" s="11">
+        <v>8300</v>
+      </c>
+      <c r="O4" s="11">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -1564,8 +2597,23 @@
       <c r="G5" s="3">
         <v>900</v>
       </c>
+      <c r="H5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5" s="11">
+        <v>100500</v>
+      </c>
+      <c r="N5" s="11">
+        <v>17300</v>
+      </c>
+      <c r="O5" s="11">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -1587,8 +2635,23 @@
       <c r="G6" s="3">
         <v>4200</v>
       </c>
+      <c r="H6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6" s="11">
+        <v>53000</v>
+      </c>
+      <c r="N6" s="11">
+        <v>10200</v>
+      </c>
+      <c r="O6" s="11">
+        <v>4</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -1610,8 +2673,11 @@
       <c r="G7" s="3">
         <v>1500</v>
       </c>
+      <c r="H7" s="10" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
@@ -1633,8 +2699,11 @@
       <c r="G8" s="3">
         <v>800</v>
       </c>
+      <c r="H8" s="10" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -1656,8 +2725,11 @@
       <c r="G9" s="3">
         <v>5500</v>
       </c>
+      <c r="H9" s="10" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
@@ -1679,8 +2751,11 @@
       <c r="G10" s="3">
         <v>2500</v>
       </c>
+      <c r="H10" s="10" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -1702,8 +2777,11 @@
       <c r="G11" s="3">
         <v>1100</v>
       </c>
+      <c r="H11" s="10" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
@@ -1725,8 +2803,11 @@
       <c r="G12" s="3">
         <v>7000</v>
       </c>
+      <c r="H12" s="10" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>32</v>
       </c>
@@ -1748,8 +2829,11 @@
       <c r="G13" s="3">
         <v>3800</v>
       </c>
+      <c r="H13" s="10" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
@@ -1771,8 +2855,11 @@
       <c r="G14" s="3">
         <v>600</v>
       </c>
+      <c r="H14" s="10" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
@@ -1794,8 +2881,11 @@
       <c r="G15" s="3">
         <v>2200</v>
       </c>
+      <c r="H15" s="10" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>38</v>
       </c>
@@ -1816,6 +2906,9 @@
       </c>
       <c r="G16" s="3">
         <v>5000</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
